--- a/templates/ManagedByInfo.xlsx
+++ b/templates/ManagedByInfo.xlsx
@@ -6,12 +6,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66E1983-8C94-4594-9F72-BFC37416FF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D5FBBA-0986-D848-B339-B6E8C6724D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26860" xr2:uid="{FDAC34F5-1D07-443C-9850-E44A0C30F262}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26860" xr2:uid="{FDAC34F5-1D07-443C-9850-E44A0C30F262}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21692,15 +21692,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5E65BBFAB17F40B7016889053DEED5" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0f6498ae099ef27475c0a1b2b6776a97">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1446b84a-9843-4b01-9b8c-869c6c75acf9" xmlns:ns3="65cf8547-cd0b-4241-876c-e2fe626ea33c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc4bac7550c43049f6f313718c500366" ns2:_="" ns3:_="">
     <xsd:import namespace="1446b84a-9843-4b01-9b8c-869c6c75acf9"/>
@@ -21984,6 +21975,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -21997,14 +21997,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A50DC656-9D14-4F70-B51F-B7A93754F1E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A2D0443-9D8C-45D2-9529-7AEB835BE570}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22019,6 +22011,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A50DC656-9D14-4F70-B51F-B7A93754F1E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/templates/ManagedByInfo.xlsx
+++ b/templates/ManagedByInfo.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D5FBBA-0986-D848-B339-B6E8C6724D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093EE3C6-0B9B-294F-8F0C-03CDCCE4220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26860" xr2:uid="{FDAC34F5-1D07-443C-9850-E44A0C30F262}"/>
   </bookViews>
